--- a/input/OCA-Input-Template.xlsx
+++ b/input/OCA-Input-Template.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:L13"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -412,6 +412,7 @@
     <col min="9" max="9" width="22.83203125" customWidth="1"/>
     <col min="10" max="10" width="16.83203125" customWidth="1"/>
     <col min="11" max="11" width="9.83203125" customWidth="1"/>
+    <col min="12" max="12" width="90.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -448,13 +449,16 @@
       <c r="K1" t="str">
         <v>Enabled</v>
       </c>
+      <c r="L1" t="str">
+        <v>Notes</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
         <v>JOB-001</v>
       </c>
       <c r="B2" t="str">
-        <v>P75399-B21</v>
+        <v>P72176-B21</v>
       </c>
       <c r="C2" t="str">
         <v>Server</v>
@@ -482,6 +486,9 @@
       </c>
       <c r="K2" t="str">
         <v>Yes</v>
+      </c>
+      <c r="L2" t="str">
+        <v>DL360 Gen12. Passed end to end.</v>
       </c>
     </row>
     <row r="3">
@@ -489,10 +496,10 @@
         <v>JOB-002</v>
       </c>
       <c r="B3" t="str">
-        <v>P72176-B21</v>
+        <v>P72297-B21</v>
       </c>
       <c r="C3" t="str">
-        <v>Nutanix</v>
+        <v>Server</v>
       </c>
       <c r="D3" t="str">
         <v/>
@@ -517,6 +524,9 @@
       </c>
       <c r="K3" t="str">
         <v>Yes</v>
+      </c>
+      <c r="L3" t="str">
+        <v>DL360-class. Passed end to end.</v>
       </c>
     </row>
     <row r="4">
@@ -524,10 +534,10 @@
         <v>JOB-003</v>
       </c>
       <c r="B4" t="str">
-        <v>S3V83A</v>
+        <v>P75219-B21</v>
       </c>
       <c r="C4" t="str">
-        <v>Solution</v>
+        <v>Server</v>
       </c>
       <c r="D4" t="str">
         <v/>
@@ -552,6 +562,9 @@
       </c>
       <c r="K4" t="str">
         <v>Yes</v>
+      </c>
+      <c r="L4" t="str">
+        <v>DL320 Gen12. Passed end to end.</v>
       </c>
     </row>
     <row r="5">
@@ -559,10 +572,10 @@
         <v>JOB-004</v>
       </c>
       <c r="B5" t="str">
-        <v>S2U63A</v>
+        <v>P75220-B21</v>
       </c>
       <c r="C5" t="str">
-        <v>Storage</v>
+        <v>Server</v>
       </c>
       <c r="D5" t="str">
         <v/>
@@ -588,17 +601,324 @@
       <c r="K5" t="str">
         <v>Yes</v>
       </c>
+      <c r="L5" t="str">
+        <v>DL320 Gen12. Passed end to end.</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>JOB-005</v>
+      </c>
+      <c r="B6" t="str">
+        <v>P75217-B21</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Server</v>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v>Random</v>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="K6" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="L6" t="str">
+        <v>DL320 Gen12. Failed on a boot device rule; repair added, retest.</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>JOB-006</v>
+      </c>
+      <c r="B7" t="str">
+        <v>P75218-B21</v>
+      </c>
+      <c r="C7" t="str">
+        <v>Server</v>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v>Random</v>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="K7" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="L7" t="str">
+        <v>DL320 Gen12. Failed on an OCP/processor rule; repair added, retest.</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>JOB-007</v>
+      </c>
+      <c r="B8" t="str">
+        <v>P86628-B21</v>
+      </c>
+      <c r="C8" t="str">
+        <v>Server</v>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v>Random</v>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+      <c r="J8" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="K8" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="L8" t="str">
+        <v>DL110 Gen12. Failed on the M.2 rule; fixed, retest.</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>JOB-008</v>
+      </c>
+      <c r="B9" t="str">
+        <v>P83540-B21</v>
+      </c>
+      <c r="C9" t="str">
+        <v>Server</v>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v>Random</v>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="K9" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="L9" t="str">
+        <v>DL580 Gen12. Failed on Smart Chassis (old build); fixed, retest.</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>JOB-009</v>
+      </c>
+      <c r="B10" t="str">
+        <v>P75399-B21</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Server</v>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v>Random</v>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="K10" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="L10" t="str">
+        <v>DL580 Gen12 SFF. Failed on non-mandatory red icons; now only Processor/Memory block, retest.</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>JOB-010</v>
+      </c>
+      <c r="B11" t="str">
+        <v>P72176-B21</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Nutanix</v>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v>Random</v>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="K11" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="L11" t="str">
+        <v>Nutanix DL360 G12. Failed in Customer Account; fixed, retest.</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>JOB-011</v>
+      </c>
+      <c r="B12" t="str">
+        <v>S3V83A</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Solution</v>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v>Random</v>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="K12" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="L12" t="str">
+        <v>dHCI solution. Wizard and Menu passed; server inside the solution added, retest.</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>JOB-012</v>
+      </c>
+      <c r="B13" t="str">
+        <v>S2U63A</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Server</v>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v>Random</v>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
+      <c r="J13" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="K13" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="L13" t="str">
+        <v>DL380 Gen11 Data Solutions. Stopped at Billing Tier; capacity entry added, retest.</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L13"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G1"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="18.83203125" customWidth="1"/>
@@ -632,62 +952,16 @@
         <v>Sequence</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>JOB-001</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Processor</v>
-      </c>
-      <c r="C2" t="str">
-        <v/>
-      </c>
-      <c r="D2" t="str">
-        <v/>
-      </c>
-      <c r="E2" t="str">
-        <v>random</v>
-      </c>
-      <c r="F2" t="str">
-        <v/>
-      </c>
-      <c r="G2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>JOB-001</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Memory</v>
-      </c>
-      <c r="C3" t="str">
-        <v/>
-      </c>
-      <c r="D3" t="str">
-        <v/>
-      </c>
-      <c r="E3" t="str">
-        <v>random</v>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3">
-        <v>20</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C21"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="34.83203125" customWidth="1"/>
@@ -839,84 +1113,95 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Components sheet</v>
+        <v>Notes</v>
       </c>
       <c r="B14" t="str">
-        <v/>
+        <v>Optional</v>
       </c>
       <c r="C14" t="str">
-        <v>Optional. A model with no rows here gets random Processor, Memory, Smart Chassis and Power Supplies. Processor and Memory are always mandatory.</v>
+        <v>Free text for the team; not read by the tool.</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Section</v>
+        <v>Components sheet</v>
       </c>
       <c r="B15" t="str">
-        <v>Required per row</v>
+        <v/>
       </c>
       <c r="C15" t="str">
-        <v>OCA Menu section title, e.g. Processor, Memory, Power Supplies.</v>
+        <v>Optional. A model with no rows here gets random Processor, Memory, Smart Chassis and Power Supplies. Processor and Memory are always mandatory.</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Product Number</v>
+        <v>Section</v>
       </c>
       <c r="B16" t="str">
-        <v>Optional</v>
+        <v>Required per row</v>
       </c>
       <c r="C16" t="str">
-        <v>Product to select, e.g. P74509-B21. Blank with Random: any product.</v>
+        <v>OCA Menu section title, e.g. Processor, Memory, Power Supplies.</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Quantity</v>
+        <v>Product Number</v>
       </c>
       <c r="B17" t="str">
         <v>Optional</v>
       </c>
       <c r="C17" t="str">
-        <v>Number to select.</v>
+        <v>Product to select, e.g. P74509-B21. Blank with Random: any product.</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Selection Type</v>
+        <v>Quantity</v>
       </c>
       <c r="B18" t="str">
-        <v>radio / quantity / random / checkbox / configuration / automatic / default</v>
+        <v>Optional</v>
       </c>
       <c r="C18" t="str">
-        <v>How the product is selected; Random picks any allowed product.</v>
+        <v>Number to select.</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Configuration Text</v>
+        <v>Selection Type</v>
       </c>
       <c r="B19" t="str">
-        <v>Optional</v>
+        <v>radio / quantity / random / checkbox / configuration / automatic / default</v>
       </c>
       <c r="C19" t="str">
-        <v>Configuration selection: the option text.</v>
+        <v>How the product is selected; Random picks any allowed product.</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Sequence</v>
+        <v>Configuration Text</v>
       </c>
       <c r="B20" t="str">
         <v>Optional</v>
       </c>
       <c r="C20" t="str">
+        <v>Configuration selection: the option text.</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>Sequence</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="C21" t="str">
         <v>Order of the rows within a model (10, 20, 30...).</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C20"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C21"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/input/OCA-Input-Template.xlsx
+++ b/input/OCA-Input-Template.xlsx
@@ -399,20 +399,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:M14"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
     <col min="3" max="3" width="12.83203125" customWidth="1"/>
     <col min="4" max="4" width="26.83203125" customWidth="1"/>
     <col min="5" max="5" width="20.83203125" customWidth="1"/>
-    <col min="6" max="6" width="13.83203125" customWidth="1"/>
-    <col min="7" max="7" width="18.83203125" customWidth="1"/>
-    <col min="8" max="8" width="26.83203125" customWidth="1"/>
-    <col min="9" max="9" width="22.83203125" customWidth="1"/>
-    <col min="10" max="10" width="16.83203125" customWidth="1"/>
-    <col min="11" max="11" width="9.83203125" customWidth="1"/>
-    <col min="12" max="12" width="90.83203125" customWidth="1"/>
+    <col min="6" max="6" width="16.83203125" customWidth="1"/>
+    <col min="7" max="7" width="13.83203125" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" customWidth="1"/>
+    <col min="9" max="9" width="26.83203125" customWidth="1"/>
+    <col min="10" max="10" width="22.83203125" customWidth="1"/>
+    <col min="11" max="11" width="16.83203125" customWidth="1"/>
+    <col min="12" max="12" width="9.83203125" customWidth="1"/>
+    <col min="13" max="13" width="90.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -432,24 +433,27 @@
         <v>Customer Account</v>
       </c>
       <c r="F1" t="str">
+        <v>Country</v>
+      </c>
+      <c r="G1" t="str">
         <v>Service Type</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>Server</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>Integration Rack Part number</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>Solution Name</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>Generate End BOM</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>Enabled</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>Notes</v>
       </c>
     </row>
@@ -470,11 +474,11 @@
         <v/>
       </c>
       <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
         <v>Random</v>
       </c>
-      <c r="G2" t="str">
-        <v/>
-      </c>
       <c r="H2" t="str">
         <v/>
       </c>
@@ -482,12 +486,15 @@
         <v/>
       </c>
       <c r="J2" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="K2" t="str">
         <v>Yes</v>
       </c>
       <c r="L2" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M2" t="str">
         <v>DL360 Gen12. Passed end to end.</v>
       </c>
     </row>
@@ -508,11 +515,11 @@
         <v/>
       </c>
       <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
         <v>Random</v>
       </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
       <c r="H3" t="str">
         <v/>
       </c>
@@ -520,12 +527,15 @@
         <v/>
       </c>
       <c r="J3" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="K3" t="str">
         <v>Yes</v>
       </c>
       <c r="L3" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M3" t="str">
         <v>DL360-class. Passed end to end.</v>
       </c>
     </row>
@@ -546,11 +556,11 @@
         <v/>
       </c>
       <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
         <v>Random</v>
       </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
       <c r="H4" t="str">
         <v/>
       </c>
@@ -558,12 +568,15 @@
         <v/>
       </c>
       <c r="J4" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="K4" t="str">
         <v>Yes</v>
       </c>
       <c r="L4" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M4" t="str">
         <v>DL320 Gen12. Passed end to end.</v>
       </c>
     </row>
@@ -584,11 +597,11 @@
         <v/>
       </c>
       <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
         <v>Random</v>
       </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
       <c r="H5" t="str">
         <v/>
       </c>
@@ -596,12 +609,15 @@
         <v/>
       </c>
       <c r="J5" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="K5" t="str">
         <v>Yes</v>
       </c>
       <c r="L5" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M5" t="str">
         <v>DL320 Gen12. Passed end to end.</v>
       </c>
     </row>
@@ -622,11 +638,11 @@
         <v/>
       </c>
       <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
         <v>Random</v>
       </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
       <c r="H6" t="str">
         <v/>
       </c>
@@ -634,12 +650,15 @@
         <v/>
       </c>
       <c r="J6" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="K6" t="str">
         <v>Yes</v>
       </c>
       <c r="L6" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M6" t="str">
         <v>DL320 Gen12. Failed on a boot device rule; repair added, retest.</v>
       </c>
     </row>
@@ -660,11 +679,11 @@
         <v/>
       </c>
       <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
         <v>Random</v>
       </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
       <c r="H7" t="str">
         <v/>
       </c>
@@ -672,12 +691,15 @@
         <v/>
       </c>
       <c r="J7" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="K7" t="str">
         <v>Yes</v>
       </c>
       <c r="L7" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M7" t="str">
         <v>DL320 Gen12. Failed on an OCP/processor rule; repair added, retest.</v>
       </c>
     </row>
@@ -698,11 +720,11 @@
         <v/>
       </c>
       <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
         <v>Random</v>
       </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
       <c r="H8" t="str">
         <v/>
       </c>
@@ -710,12 +732,15 @@
         <v/>
       </c>
       <c r="J8" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="K8" t="str">
         <v>Yes</v>
       </c>
       <c r="L8" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M8" t="str">
         <v>DL110 Gen12. Failed on the M.2 rule; fixed, retest.</v>
       </c>
     </row>
@@ -736,11 +761,11 @@
         <v/>
       </c>
       <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
         <v>Random</v>
       </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
       <c r="H9" t="str">
         <v/>
       </c>
@@ -748,12 +773,15 @@
         <v/>
       </c>
       <c r="J9" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="K9" t="str">
         <v>Yes</v>
       </c>
       <c r="L9" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M9" t="str">
         <v>DL580 Gen12. Failed on Smart Chassis (old build); fixed, retest.</v>
       </c>
     </row>
@@ -774,11 +802,11 @@
         <v/>
       </c>
       <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
         <v>Random</v>
       </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
       <c r="H10" t="str">
         <v/>
       </c>
@@ -786,12 +814,15 @@
         <v/>
       </c>
       <c r="J10" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="K10" t="str">
         <v>Yes</v>
       </c>
       <c r="L10" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M10" t="str">
         <v>DL580 Gen12 SFF. Failed on non-mandatory red icons; now only Processor/Memory block, retest.</v>
       </c>
     </row>
@@ -812,11 +843,11 @@
         <v/>
       </c>
       <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
         <v>Random</v>
       </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
       <c r="H11" t="str">
         <v/>
       </c>
@@ -824,12 +855,15 @@
         <v/>
       </c>
       <c r="J11" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="K11" t="str">
         <v>Yes</v>
       </c>
       <c r="L11" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M11" t="str">
         <v>Nutanix DL360 G12. Failed in Customer Account; fixed, retest.</v>
       </c>
     </row>
@@ -850,11 +884,11 @@
         <v/>
       </c>
       <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
         <v>Random</v>
       </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
       <c r="H12" t="str">
         <v/>
       </c>
@@ -862,12 +896,15 @@
         <v/>
       </c>
       <c r="J12" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="K12" t="str">
         <v>Yes</v>
       </c>
       <c r="L12" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M12" t="str">
         <v>dHCI solution. Wizard and Menu passed; server inside the solution added, retest.</v>
       </c>
     </row>
@@ -888,11 +925,11 @@
         <v/>
       </c>
       <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
         <v>Random</v>
       </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
       <c r="H13" t="str">
         <v/>
       </c>
@@ -900,18 +937,62 @@
         <v/>
       </c>
       <c r="J13" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="K13" t="str">
         <v>Yes</v>
       </c>
       <c r="L13" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M13" t="str">
         <v>DL380 Gen11 Data Solutions. Stopped at Billing Tier; capacity entry added, retest.</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>JOB-013</v>
+      </c>
+      <c r="B14" t="str">
+        <v>S3V83A</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Solution</v>
+      </c>
+      <c r="D14" t="str">
+        <v>HPE GreenLake for PC3000 with Alletra Storage MP (Block)</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v>SAUDI ARABIA</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Random</v>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="L14" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M14" t="str">
+        <v>Arcus dHCI solution in Saudi Arabia (same product as JOB-011). New: Country; retest.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M14"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -961,7 +1042,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C22"/>
   <cols>
     <col min="1" max="1" width="28.83203125" customWidth="1"/>
     <col min="2" max="2" width="34.83203125" customWidth="1"/>
@@ -1047,161 +1128,172 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Service Type</v>
+        <v>Country</v>
       </c>
       <c r="B8" t="str">
         <v>Optional</v>
       </c>
       <c r="C8" t="str">
-        <v>Random (default) or the service experience to select.</v>
+        <v>Landing page Country, as OCA lists it (e.g. SAUDI ARABIA) or its code (SA). Blank: UNITED STATES.</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Server</v>
+        <v>Service Type</v>
       </c>
       <c r="B9" t="str">
         <v>Optional</v>
       </c>
       <c r="C9" t="str">
-        <v>Solution models: the server to pick in the Solution Wizard.</v>
+        <v>Random (default) or the service experience to select.</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Integration Rack Part number</v>
+        <v>Server</v>
       </c>
       <c r="B10" t="str">
         <v>Optional</v>
       </c>
       <c r="C10" t="str">
-        <v>Blank: Standalone. Yes: any rack. Or the rack option text.</v>
+        <v>Solution models: the server to pick in the Solution Wizard.</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Solution Name</v>
+        <v>Integration Rack Part number</v>
       </c>
       <c r="B11" t="str">
         <v>Optional</v>
       </c>
       <c r="C11" t="str">
-        <v>Solution models: the solution to pick in the Solution Wizard.</v>
+        <v>Blank: Standalone. Yes: any rack. Or the rack option text.</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Generate End BOM</v>
+        <v>Solution Name</v>
       </c>
       <c r="B12" t="str">
-        <v>Yes / No</v>
+        <v>Optional</v>
       </c>
       <c r="C12" t="str">
-        <v>Default Yes.</v>
+        <v>Solution models: the solution to pick in the Solution Wizard.</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Enabled</v>
+        <v>Generate End BOM</v>
       </c>
       <c r="B13" t="str">
         <v>Yes / No</v>
       </c>
       <c r="C13" t="str">
-        <v>Default Yes. No: the row is skipped.</v>
+        <v>Default Yes.</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Notes</v>
+        <v>Enabled</v>
       </c>
       <c r="B14" t="str">
-        <v>Optional</v>
+        <v>Yes / No</v>
       </c>
       <c r="C14" t="str">
-        <v>Free text for the team; not read by the tool.</v>
+        <v>Default Yes. No: the row is skipped.</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Components sheet</v>
+        <v>Notes</v>
       </c>
       <c r="B15" t="str">
-        <v/>
+        <v>Optional</v>
       </c>
       <c r="C15" t="str">
-        <v>Optional. A model with no rows here gets random Processor, Memory, Smart Chassis and Power Supplies. Processor and Memory are always mandatory.</v>
+        <v>Free text for the team; not read by the tool.</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Section</v>
+        <v>Components sheet</v>
       </c>
       <c r="B16" t="str">
-        <v>Required per row</v>
+        <v/>
       </c>
       <c r="C16" t="str">
-        <v>OCA Menu section title, e.g. Processor, Memory, Power Supplies.</v>
+        <v>Optional. A model with no rows here gets random Processor, Memory, Smart Chassis and Power Supplies. Processor and Memory are always mandatory.</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Product Number</v>
+        <v>Section</v>
       </c>
       <c r="B17" t="str">
-        <v>Optional</v>
+        <v>Required per row</v>
       </c>
       <c r="C17" t="str">
-        <v>Product to select, e.g. P74509-B21. Blank with Random: any product.</v>
+        <v>OCA Menu section title, e.g. Processor, Memory, Power Supplies.</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Quantity</v>
+        <v>Product Number</v>
       </c>
       <c r="B18" t="str">
         <v>Optional</v>
       </c>
       <c r="C18" t="str">
-        <v>Number to select.</v>
+        <v>Product to select, e.g. P74509-B21. Blank with Random: any product.</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Selection Type</v>
+        <v>Quantity</v>
       </c>
       <c r="B19" t="str">
-        <v>radio / quantity / random / checkbox / configuration / automatic / default</v>
+        <v>Optional</v>
       </c>
       <c r="C19" t="str">
-        <v>How the product is selected; Random picks any allowed product.</v>
+        <v>Number to select.</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Configuration Text</v>
+        <v>Selection Type</v>
       </c>
       <c r="B20" t="str">
-        <v>Optional</v>
+        <v>radio / quantity / random / checkbox / configuration / automatic / default</v>
       </c>
       <c r="C20" t="str">
-        <v>Configuration selection: the option text.</v>
+        <v>How the product is selected; Random picks any allowed product.</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Sequence</v>
+        <v>Configuration Text</v>
       </c>
       <c r="B21" t="str">
         <v>Optional</v>
       </c>
       <c r="C21" t="str">
+        <v>Configuration selection: the option text.</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Sequence</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Optional</v>
+      </c>
+      <c r="C22" t="str">
         <v>Order of the rows within a model (10, 20, 30...).</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C22"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/input/OCA-Input-Template.xlsx
+++ b/input/OCA-Input-Template.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -990,9 +990,50 @@
         <v>Arcus dHCI solution in Saudi Arabia (same product as JOB-011). New: Country; retest.</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>JOB-014</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Private</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Arcus EMEA</v>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v>Random</v>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="L15" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M15" t="str">
+        <v>Arcus EMEA preset: Saudi Arabia and the Arcus description filled in. New; test.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M15"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1098,10 +1139,10 @@
         <v>Model Type</v>
       </c>
       <c r="B5" t="str">
-        <v>Server / Solution / Storage / Nutanix or blank</v>
+        <v>Server / Solution / Storage / Nutanix / Arcus EMEA or blank</v>
       </c>
       <c r="C5" t="str">
-        <v>Server: Menu tab. Solution: Solution Wizard. Storage: storage flow. Nutanix: Customer Account set to Nutanix in Advanced Settings, the search result containing "Nutanix" is opened, then the Server route. Blank: detected from OCA.</v>
+        <v>Server: Menu tab. Solution: Solution Wizard. Storage: storage flow. Nutanix: Customer Account set to Nutanix in Advanced Settings, the search result containing "Nutanix" is opened, then the Server route. Arcus EMEA: the Arcus solution (HPE GreenLake for PC3000 with Alletra Storage MP (Block)) in SAUDI ARABIA, built in its Wizard; Model Number is the search word, e.g. Private. Blank: detected from OCA.</v>
       </c>
     </row>
     <row r="6">
@@ -1112,7 +1153,7 @@
         <v>Optional</v>
       </c>
       <c r="C6" t="str">
-        <v>Text the OCA search result must contain, when the model has several results. Nutanix models use "Nutanix" when blank.</v>
+        <v>Text the OCA search result must contain, when the model has several results. Nutanix models use "Nutanix" when blank; Arcus EMEA uses the Arcus solution name.</v>
       </c>
     </row>
     <row r="7">
@@ -1134,7 +1175,7 @@
         <v>Optional</v>
       </c>
       <c r="C8" t="str">
-        <v>Landing page Country, as OCA lists it (e.g. SAUDI ARABIA) or its code (SA). Blank: UNITED STATES.</v>
+        <v>Landing page Country, as OCA lists it (e.g. SAUDI ARABIA) or its code (SA). Blank: UNITED STATES (Arcus EMEA: SAUDI ARABIA).</v>
       </c>
     </row>
     <row r="9">

--- a/input/OCA-Input-Template.xlsx
+++ b/input/OCA-Input-Template.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M17"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -1031,9 +1031,91 @@
         <v>Arcus EMEA preset: Saudi Arabia and the Arcus description filled in. New; test.</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>JOB-015</v>
+      </c>
+      <c r="B16" t="str">
+        <v>S8J33A</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Simplivity Wizard</v>
+      </c>
+      <c r="D16" t="str">
+        <v/>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v>Random</v>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v/>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="L16" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M16" t="str">
+        <v>SimpliVity 380 Gen12 in its Wizard. New; test.</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>JOB-016</v>
+      </c>
+      <c r="B17" t="str">
+        <v>S2V31A</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Simplivity Wizard</v>
+      </c>
+      <c r="D17" t="str">
+        <v/>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v>Random</v>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="L17" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M17" t="str">
+        <v>SimpliVity 325 Gen11 in its Wizard. New; test.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M17"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1139,10 +1221,10 @@
         <v>Model Type</v>
       </c>
       <c r="B5" t="str">
-        <v>Server / Solution / Storage / Nutanix / Arcus EMEA or blank</v>
+        <v>Server / Solution / Storage / Nutanix / Arcus EMEA / Simplivity Wizard or blank</v>
       </c>
       <c r="C5" t="str">
-        <v>Server: Menu tab. Solution: Solution Wizard. Storage: storage flow. Nutanix: Customer Account set to Nutanix in Advanced Settings, the search result containing "Nutanix" is opened, then the Server route. Arcus EMEA: the Arcus solution (HPE GreenLake for PC3000 with Alletra Storage MP (Block)) in SAUDI ARABIA, built in its Wizard; Model Number is the search word, e.g. Private. Blank: detected from OCA.</v>
+        <v>Server: Menu tab. Solution: Solution Wizard. Storage: storage flow. Nutanix: Customer Account set to Nutanix in Advanced Settings, the search result containing "Nutanix" is opened, then the Server route. Arcus EMEA: the Arcus solution (HPE GreenLake for PC3000 with Alletra Storage MP (Block)) in SAUDI ARABIA, built in its Wizard; Model Number is the search word, e.g. Private. Simplivity Wizard: the Wizard card of the model is opened (not its CTO card); Processor and Memory are picked, then every wizard dropdown still asking for a selection, at the minimum quantity its messages state. Blank: detected from OCA.</v>
       </c>
     </row>
     <row r="6">

--- a/input/OCA-Input-Template.xlsx
+++ b/input/OCA-Input-Template.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M17"/>
+  <dimension ref="A1:M19"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -1113,9 +1113,91 @@
         <v>SimpliVity 325 Gen11 in its Wizard. New; test.</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>JOB-017</v>
+      </c>
+      <c r="B18" t="str">
+        <v>4000</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Alletra 4000</v>
+      </c>
+      <c r="D18" t="str">
+        <v/>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v>Random</v>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="L18" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M18" t="str">
+        <v>HPE Alletra Storage Servers in their wizard. New; test.</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>JOB-018</v>
+      </c>
+      <c r="B19" t="str">
+        <v>alletra</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Alletra 5000</v>
+      </c>
+      <c r="D19" t="str">
+        <v/>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v>Random</v>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v/>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="L19" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M19" t="str">
+        <v>HPE Alletra 5000 array in the Alletra5000Sol Wizard. New; test.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M19"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1221,10 +1303,10 @@
         <v>Model Type</v>
       </c>
       <c r="B5" t="str">
-        <v>Server / Solution / Storage / Nutanix / Arcus EMEA / Simplivity Wizard or blank</v>
+        <v>Server / Solution / Storage / Nutanix / Arcus EMEA / Simplivity Wizard / Alletra 4000 / Alletra 5000 or blank</v>
       </c>
       <c r="C5" t="str">
-        <v>Server: Menu tab. Solution: Solution Wizard. Storage: storage flow. Nutanix: Customer Account set to Nutanix in Advanced Settings, the search result containing "Nutanix" is opened, then the Server route. Arcus EMEA: the Arcus solution (HPE GreenLake for PC3000 with Alletra Storage MP (Block)) in SAUDI ARABIA, built in its Wizard; Model Number is the search word, e.g. Private. Simplivity Wizard: the Wizard card of the model is opened (not its CTO card); Processor and Memory are picked, then every wizard dropdown still asking for a selection, at the minimum quantity its messages state. Blank: detected from OCA.</v>
+        <v>Server: Menu tab. Solution: Solution Wizard. Storage: storage flow. Nutanix: Customer Account set to Nutanix in Advanced Settings, the search result containing "Nutanix" is opened, then the Server route. Arcus EMEA: the Arcus solution (HPE GreenLake for PC3000 with Alletra Storage MP (Block)) in SAUDI ARABIA, built in its Wizard; Model Number is the search word, e.g. Private. Simplivity Wizard: the Wizard card of the model is opened (not its CTO card); Processor and Memory are picked, then every wizard dropdown still asking for a selection, at the minimum quantity its messages state. Alletra 4000 / Alletra 5000: the "HPE Alletra Storage Servers" / "HPE Alletra 5000" search result (Model Number is the search word, e.g. 4000 / alletra), built in its wizard: the base model first, then each wizard tab's mandatory dropdowns. Blank: detected from OCA.</v>
       </c>
     </row>
     <row r="6">

--- a/input/OCA-Input-Template.xlsx
+++ b/input/OCA-Input-Template.xlsx
@@ -1151,7 +1151,7 @@
         <v>Yes</v>
       </c>
       <c r="M18" t="str">
-        <v>HPE Alletra Storage Servers in their wizard. New; test.</v>
+        <v>HPE Alletra Storage Servers in their wizard. Passed (2026-10-22).</v>
       </c>
     </row>
     <row r="19">
@@ -1192,7 +1192,7 @@
         <v>Yes</v>
       </c>
       <c r="M19" t="str">
-        <v>HPE Alletra 5000 array in the Alletra5000Sol Wizard. New; test.</v>
+        <v>HPE Alletra 5000 array in the Alletra5000Sol Wizard. Passed (2026-10-22).</v>
       </c>
     </row>
   </sheetData>

--- a/input/OCA-Input-Template.xlsx
+++ b/input/OCA-Input-Template.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M21"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -1195,9 +1195,91 @@
         <v>HPE Alletra 5000 array in the Alletra5000Sol Wizard. Passed (2026-10-22).</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>JOB-019</v>
+      </c>
+      <c r="B20" t="str">
+        <v>S1F24A</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Storage</v>
+      </c>
+      <c r="D20" t="str">
+        <v/>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v>Random</v>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v/>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="L20" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M20" t="str">
+        <v>HPE GreenLake for File ("razercrestsol" CTO): Cloud Connectivity, Site Survey, Capacity. New; test.</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>JOB-020</v>
+      </c>
+      <c r="B21" t="str">
+        <v>P97048-B21</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Server</v>
+      </c>
+      <c r="D21" t="str">
+        <v/>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v>Random</v>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v/>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="L21" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="M21" t="str">
+        <v>DL585a Gen13: every processor over 270W; the lowest power is taken. Retest.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M21"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1306,7 +1388,7 @@
         <v>Server / Solution / Storage / Nutanix / Arcus EMEA / Simplivity Wizard / Alletra 4000 / Alletra 5000 or blank</v>
       </c>
       <c r="C5" t="str">
-        <v>Server: Menu tab. Solution: Solution Wizard. Storage: storage flow. Nutanix: Customer Account set to Nutanix in Advanced Settings, the search result containing "Nutanix" is opened, then the Server route. Arcus EMEA: the Arcus solution (HPE GreenLake for PC3000 with Alletra Storage MP (Block)) in SAUDI ARABIA, built in its Wizard; Model Number is the search word, e.g. Private. Simplivity Wizard: the Wizard card of the model is opened (not its CTO card); Processor and Memory are picked, then every wizard dropdown still asking for a selection, at the minimum quantity its messages state. Alletra 4000 / Alletra 5000: the "HPE Alletra Storage Servers" / "HPE Alletra 5000" search result (Model Number is the search word, e.g. 4000 / alletra), built in its wizard: the base model first, then each wizard tab's mandatory dropdowns. Blank: detected from OCA.</v>
+        <v>Server: Menu tab. Solution: Solution Wizard. Storage: storage flow (Cloud Connectivity, Controller Nodes or Site Survey, Capacity; e.g. S1F24A). Nutanix: Customer Account set to Nutanix in Advanced Settings, the search result containing "Nutanix" is opened, then the Server route. Arcus EMEA: the Arcus solution (HPE GreenLake for PC3000 with Alletra Storage MP (Block)) in SAUDI ARABIA, built in its Wizard; Model Number is the search word, e.g. Private. Simplivity Wizard: the Wizard card of the model is opened (not its CTO card); Processor and Memory are picked, then every wizard dropdown still asking for a selection, at the minimum quantity its messages state. Alletra 4000 / Alletra 5000: the "HPE Alletra Storage Servers" / "HPE Alletra 5000" search result (Model Number is the search word, e.g. 4000 / alletra), built in its wizard: the base model first, then each wizard tab's mandatory dropdowns. Blank: detected from OCA.</v>
       </c>
     </row>
     <row r="6">
